--- a/Collections/EURO/Germany/#EURO#Germany#Commemorative#[2006-present]#UNC.xlsx
+++ b/Collections/EURO/Germany/#EURO#Germany#Commemorative#[2006-present]#UNC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42E2F90-51C6-4A77-86A4-F62770160CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B799B9A-3B1F-43F8-B627-C49B2ECF1C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="1430" windowWidth="33150" windowHeight="17560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2€" sheetId="1" r:id="rId1"/>
@@ -209,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="219">
   <si>
     <t>Year</t>
   </si>
@@ -833,6 +833,39 @@
   </si>
   <si>
     <t>German Unification</t>
+  </si>
+  <si>
+    <t>6th page</t>
+  </si>
+  <si>
+    <t>Bremen, Climate House</t>
+  </si>
+  <si>
+    <t>Konrad Adenauer</t>
+  </si>
+  <si>
+    <t>6.000.000</t>
+  </si>
+  <si>
+    <t>6.300.000</t>
+  </si>
+  <si>
+    <t>7.200.000</t>
+  </si>
+  <si>
+    <t>4.200.000</t>
+  </si>
+  <si>
+    <t>6.033.000</t>
+  </si>
+  <si>
+    <t>6.333.000</t>
+  </si>
+  <si>
+    <t>7.233.000</t>
+  </si>
+  <si>
+    <t>4.233.000</t>
   </si>
 </sst>
 </file>
@@ -1227,7 +1260,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1329,10 +1362,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1419,7 +1448,23 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1554,9 +1599,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1825,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q37"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="7" customWidth="1"/>
@@ -1838,35 +1883,35 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="23"/>
-      <c r="C1" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="58"/>
-      <c r="E1" s="59"/>
-      <c r="F1" s="60" t="s">
+      <c r="C1" s="55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="56"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="63" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="64"/>
-      <c r="M1" s="64"/>
-      <c r="N1" s="64"/>
-      <c r="O1" s="64"/>
+      <c r="L1" s="62"/>
+      <c r="M1" s="62"/>
+      <c r="N1" s="62"/>
+      <c r="O1" s="62"/>
       <c r="P1" s="23" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="56"/>
+      <c r="A2" s="54"/>
       <c r="B2" s="23" t="s">
         <v>184</v>
       </c>
@@ -1909,7 +1954,7 @@
       <c r="O2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="54" t="s">
+      <c r="P2" s="52" t="s">
         <v>205</v>
       </c>
       <c r="Q2" s="21"/>
@@ -2326,7 +2371,7 @@
       <c r="O10" s="34">
         <v>1</v>
       </c>
-      <c r="P10" s="51" t="s">
+      <c r="P10" s="49" t="s">
         <v>186</v>
       </c>
       <c r="Q10" s="16" t="str">
@@ -2380,7 +2425,7 @@
       <c r="O11" s="6">
         <v>1</v>
       </c>
-      <c r="P11" s="52"/>
+      <c r="P11" s="50"/>
       <c r="Q11" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2432,7 +2477,7 @@
       <c r="O12" s="6">
         <v>1</v>
       </c>
-      <c r="P12" s="52"/>
+      <c r="P12" s="50"/>
       <c r="Q12" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2484,7 +2529,7 @@
       <c r="O13" s="6">
         <v>1</v>
       </c>
-      <c r="P13" s="52"/>
+      <c r="P13" s="50"/>
       <c r="Q13" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2536,7 +2581,7 @@
       <c r="O14" s="6">
         <v>1</v>
       </c>
-      <c r="P14" s="52"/>
+      <c r="P14" s="50"/>
       <c r="Q14" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2588,59 +2633,59 @@
       <c r="O15" s="6">
         <v>1</v>
       </c>
-      <c r="P15" s="52"/>
+      <c r="P15" s="50"/>
       <c r="Q15" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="40">
+      <c r="A16" s="38">
         <v>2014</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="C16" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="F16" s="42" t="s">
         <v>75</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="H16" s="44" t="s">
+      <c r="H16" s="42" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="44" t="s">
+      <c r="I16" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="J16" s="44" t="s">
+      <c r="J16" s="42" t="s">
         <v>76</v>
       </c>
-      <c r="K16" s="45">
-        <v>1</v>
-      </c>
-      <c r="L16" s="45">
-        <v>1</v>
-      </c>
-      <c r="M16" s="45">
-        <v>1</v>
-      </c>
-      <c r="N16" s="45">
-        <v>1</v>
-      </c>
-      <c r="O16" s="45">
-        <v>1</v>
-      </c>
-      <c r="P16" s="53"/>
+      <c r="K16" s="43">
+        <v>1</v>
+      </c>
+      <c r="L16" s="43">
+        <v>1</v>
+      </c>
+      <c r="M16" s="43">
+        <v>1</v>
+      </c>
+      <c r="N16" s="43">
+        <v>1</v>
+      </c>
+      <c r="O16" s="43">
+        <v>1</v>
+      </c>
+      <c r="P16" s="51"/>
       <c r="Q16" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2692,7 +2737,7 @@
       <c r="O17" s="34">
         <v>1</v>
       </c>
-      <c r="P17" s="48" t="s">
+      <c r="P17" s="46" t="s">
         <v>187</v>
       </c>
       <c r="Q17" s="16" t="str">
@@ -2744,7 +2789,7 @@
       <c r="O18" s="6">
         <v>1</v>
       </c>
-      <c r="P18" s="49"/>
+      <c r="P18" s="47"/>
       <c r="Q18" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2796,7 +2841,7 @@
       <c r="O19" s="6">
         <v>1</v>
       </c>
-      <c r="P19" s="49"/>
+      <c r="P19" s="47"/>
       <c r="Q19" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2848,7 +2893,7 @@
       <c r="O20" s="6">
         <v>1</v>
       </c>
-      <c r="P20" s="49"/>
+      <c r="P20" s="47"/>
       <c r="Q20" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2900,7 +2945,7 @@
       <c r="O21" s="6">
         <v>1</v>
       </c>
-      <c r="P21" s="49"/>
+      <c r="P21" s="47"/>
       <c r="Q21" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -2950,59 +2995,59 @@
       <c r="O22" s="6">
         <v>1</v>
       </c>
-      <c r="P22" s="49"/>
+      <c r="P22" s="47"/>
       <c r="Q22" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="40">
+      <c r="A23" s="38">
         <v>2018</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="39" t="s">
         <v>132</v>
       </c>
-      <c r="C23" s="43" t="s">
+      <c r="C23" s="41" t="s">
         <v>119</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="42" t="s">
         <v>103</v>
       </c>
-      <c r="G23" s="44" t="s">
+      <c r="G23" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="H23" s="44" t="s">
+      <c r="H23" s="42" t="s">
         <v>105</v>
       </c>
-      <c r="I23" s="44" t="s">
+      <c r="I23" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="J23" s="44" t="s">
+      <c r="J23" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="K23" s="45">
-        <v>1</v>
-      </c>
-      <c r="L23" s="45">
-        <v>1</v>
-      </c>
-      <c r="M23" s="45">
-        <v>1</v>
-      </c>
-      <c r="N23" s="45">
+      <c r="K23" s="43">
+        <v>1</v>
+      </c>
+      <c r="L23" s="43">
+        <v>1</v>
+      </c>
+      <c r="M23" s="43">
+        <v>1</v>
+      </c>
+      <c r="N23" s="43">
         <v>2</v>
       </c>
-      <c r="O23" s="45">
-        <v>1</v>
-      </c>
-      <c r="P23" s="50"/>
+      <c r="O23" s="43">
+        <v>1</v>
+      </c>
+      <c r="P23" s="48"/>
       <c r="Q23" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
@@ -3052,7 +3097,7 @@
       <c r="O24" s="34">
         <v>1</v>
       </c>
-      <c r="P24" s="47" t="s">
+      <c r="P24" s="45" t="s">
         <v>188</v>
       </c>
       <c r="Q24" s="16" t="str">
@@ -3104,7 +3149,7 @@
       <c r="O25" s="6">
         <v>1</v>
       </c>
-      <c r="P25" s="39"/>
+      <c r="P25" s="37"/>
       <c r="Q25" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3156,7 +3201,7 @@
       <c r="O26" s="6">
         <v>1</v>
       </c>
-      <c r="P26" s="39"/>
+      <c r="P26" s="37"/>
       <c r="Q26" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3206,7 +3251,7 @@
       <c r="O27" s="6">
         <v>1</v>
       </c>
-      <c r="P27" s="39"/>
+      <c r="P27" s="37"/>
       <c r="Q27" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3258,7 +3303,7 @@
       <c r="O28" s="6">
         <v>1</v>
       </c>
-      <c r="P28" s="39"/>
+      <c r="P28" s="37"/>
       <c r="Q28" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
@@ -3310,59 +3355,59 @@
       <c r="O29" s="6">
         <v>1</v>
       </c>
-      <c r="P29" s="39"/>
+      <c r="P29" s="37"/>
       <c r="Q29" s="16" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="40">
+      <c r="A30" s="38">
         <v>2022</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="C30" s="42" t="s">
+      <c r="C30" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="42" t="s">
         <v>157</v>
       </c>
-      <c r="G30" s="44" t="s">
+      <c r="G30" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="H30" s="44" t="s">
+      <c r="H30" s="42" t="s">
         <v>161</v>
       </c>
-      <c r="I30" s="44" t="s">
+      <c r="I30" s="42" t="s">
         <v>163</v>
       </c>
-      <c r="J30" s="44" t="s">
+      <c r="J30" s="42" t="s">
         <v>159</v>
       </c>
-      <c r="K30" s="45">
-        <v>1</v>
-      </c>
-      <c r="L30" s="45">
+      <c r="K30" s="43">
+        <v>1</v>
+      </c>
+      <c r="L30" s="43">
         <v>2</v>
       </c>
-      <c r="M30" s="45">
-        <v>1</v>
-      </c>
-      <c r="N30" s="45">
-        <v>1</v>
-      </c>
-      <c r="O30" s="45">
-        <v>1</v>
-      </c>
-      <c r="P30" s="46"/>
+      <c r="M30" s="43">
+        <v>1</v>
+      </c>
+      <c r="N30" s="43">
+        <v>1</v>
+      </c>
+      <c r="O30" s="43">
+        <v>1</v>
+      </c>
+      <c r="P30" s="44"/>
       <c r="Q30" s="16" t="str">
         <f t="shared" si="0"/>
         <v>Can exchange</v>
@@ -3640,11 +3685,21 @@
       <c r="E36" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5"/>
-      <c r="J36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>216</v>
+      </c>
       <c r="K36" s="6">
         <v>1</v>
       </c>
@@ -3667,26 +3722,126 @@
       </c>
     </row>
     <row r="37" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="37"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37"/>
-      <c r="J37" s="37"/>
-      <c r="K37" s="37"/>
-      <c r="L37" s="37"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="38"/>
+      <c r="A37" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="K37" s="6">
+        <v>0</v>
+      </c>
+      <c r="L37" s="6">
+        <v>0</v>
+      </c>
+      <c r="M37" s="6">
+        <v>0</v>
+      </c>
+      <c r="N37" s="6">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6">
+        <v>0</v>
+      </c>
+      <c r="P37" s="36"/>
       <c r="Q37" s="16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="Q37:Q38" si="1">IF(OR(AND(K37&gt;1,K37&lt;&gt;"-"),AND(L37&gt;1,L37&lt;&gt;"-"),AND(M37&gt;1,M37&lt;&gt;"-"),AND(N37&gt;1,N37&lt;&gt;"-"),AND(O37&gt;1,O37&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
+    </row>
+    <row r="38" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="30">
+        <v>2026</v>
+      </c>
+      <c r="B38" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="32" t="s">
+        <v>136</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="G38" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>213</v>
+      </c>
+      <c r="I38" s="33" t="s">
+        <v>214</v>
+      </c>
+      <c r="J38" s="33" t="s">
+        <v>212</v>
+      </c>
+      <c r="K38" s="34">
+        <v>1</v>
+      </c>
+      <c r="L38" s="34">
+        <v>1</v>
+      </c>
+      <c r="M38" s="34">
+        <v>1</v>
+      </c>
+      <c r="N38" s="34">
+        <v>1</v>
+      </c>
+      <c r="O38" s="34">
+        <v>1</v>
+      </c>
+      <c r="P38" s="49" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q38" s="16" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P39" s="50"/>
+    </row>
+    <row r="40" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P40" s="50"/>
+    </row>
+    <row r="41" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P41" s="50"/>
+    </row>
+    <row r="42" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P42" s="50"/>
+    </row>
+    <row r="43" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P43" s="50"/>
+    </row>
+    <row r="44" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P44" s="51"/>
     </row>
   </sheetData>
   <autoFilter ref="B2:J2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -3697,8 +3852,38 @@
     <mergeCell ref="K1:O1"/>
   </mergeCells>
   <conditionalFormatting sqref="K3:O6 K8:O26">
+    <cfRule type="containsText" dxfId="17" priority="39" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K27:O27">
+    <cfRule type="containsText" dxfId="16" priority="37" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K28:O28 K30:O30 K32:O32">
     <cfRule type="containsText" dxfId="15" priority="35" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K3))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K28))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="36">
       <colorScale>
@@ -3711,9 +3896,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K27:O27">
+  <conditionalFormatting sqref="K29:O29 K31:O31">
     <cfRule type="containsText" dxfId="14" priority="33" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K27))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K29))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="34">
       <colorScale>
@@ -3726,9 +3911,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K28:O28 K30:O30 K32:O32">
+  <conditionalFormatting sqref="K34:O34">
     <cfRule type="containsText" dxfId="13" priority="31" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K28))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K34))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="32">
       <colorScale>
@@ -3741,9 +3926,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K29:O29 K31:O31">
+  <conditionalFormatting sqref="K33:O33">
     <cfRule type="containsText" dxfId="12" priority="29" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K29))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K33))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="30">
       <colorScale>
@@ -3756,9 +3941,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K34:O34">
+  <conditionalFormatting sqref="K7">
     <cfRule type="containsText" dxfId="11" priority="27" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K34))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="28">
       <colorScale>
@@ -3771,9 +3956,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K33:O33">
+  <conditionalFormatting sqref="L7">
     <cfRule type="containsText" dxfId="10" priority="25" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K33))))</formula>
+      <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="26">
       <colorScale>
@@ -3786,11 +3971,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K7">
-    <cfRule type="containsText" dxfId="9" priority="23" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K7))))</formula>
+  <conditionalFormatting sqref="O7">
+    <cfRule type="containsText" dxfId="9" priority="19" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(O7))))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="24">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3801,24 +3986,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L7">
-    <cfRule type="containsText" dxfId="8" priority="21" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(L7))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O7">
-    <cfRule type="containsText" dxfId="7" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(O7))))</formula>
+  <conditionalFormatting sqref="M7">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="16">
       <colorScale>
@@ -3831,26 +4001,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M7">
-    <cfRule type="containsText" dxfId="6" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(M7))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="N7">
-    <cfRule type="containsText" dxfId="5" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(N7))))</formula>
     </cfRule>
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3862,8 +4017,38 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K35:O35">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K35))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K36:O36">
+    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K36))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K37:O37">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K37))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -3876,9 +4061,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K36:O36">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(K36))))</formula>
+  <conditionalFormatting sqref="K38:O38">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(K38))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>

--- a/Collections/EURO/Germany/#EURO#Germany#Commemorative#[2006-present]#UNC.xlsx
+++ b/Collections/EURO/Germany/#EURO#Germany#Commemorative#[2006-present]#UNC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Germany\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B799B9A-3B1F-43F8-B627-C49B2ECF1C5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5E459D-D9E7-4C79-9267-553ECB24C20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1450,6 +1450,15 @@
   </cellStyles>
   <dxfs count="18">
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF9BE5FF"/>
@@ -1464,15 +1473,6 @@
           <bgColor rgb="FF9BE5FF"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1599,9 +1599,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="3" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="P4" s="20"/>
       <c r="Q4" s="16" t="str">
-        <f t="shared" ref="Q4:Q37" si="0">IF(OR(AND(K4&gt;1,K4&lt;&gt;"-"),AND(L4&gt;1,L4&lt;&gt;"-"),AND(M4&gt;1,M4&lt;&gt;"-"),AND(N4&gt;1,N4&lt;&gt;"-"),AND(O4&gt;1,O4&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="Q4:Q36" si="0">IF(OR(AND(K4&gt;1,K4&lt;&gt;"-"),AND(L4&gt;1,L4&lt;&gt;"-"),AND(M4&gt;1,M4&lt;&gt;"-"),AND(N4&gt;1,N4&lt;&gt;"-"),AND(O4&gt;1,O4&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3753,19 +3753,19 @@
         <v>212</v>
       </c>
       <c r="K37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="36"/>
       <c r="Q37" s="16" t="str">
@@ -4047,7 +4047,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K37:O37">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K37))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -4062,7 +4062,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K38:O38">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(K38))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
